--- a/docs/d/F/inyear.xlsx
+++ b/docs/d/F/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 102 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 97 clubs short</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1742,8 +1742,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -2296,13 +2296,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>4</v>
       </c>
       <c r="W16" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16" s="9" t="n">
         <v>1</v>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4404,8 +4404,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7979,8 +7979,8 @@
       <c r="Y71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" s="9" t="n">
-        <v>0</v>
+      <c r="Z71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="10" t="n">
         <v>1</v>
@@ -15626,7 +15626,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15696,8 +15696,8 @@
       <c r="Y148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z148" s="9" t="n">
-        <v>0</v>
+      <c r="Z148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA148" s="10" t="n">
         <v>1</v>
@@ -16333,13 +16333,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>2</v>
       </c>
       <c r="V155" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W155" s="9" t="n">
         <v>0</v>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -18144,14 +18144,14 @@
       <c r="P173" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q173" s="9" t="n">
-        <v>1</v>
+      <c r="Q173" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R173" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S173" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T173" s="10" t="n">
         <v>1</v>
@@ -21269,7 +21269,7 @@
         </is>
       </c>
       <c r="E205" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F205" s="6" t="n">
         <v>10</v>
@@ -21339,8 +21339,8 @@
       <c r="Y205" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z205" s="9" t="n">
-        <v>0</v>
+      <c r="Z205" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA205" s="10" t="n">
         <v>1</v>
@@ -22459,7 +22459,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -22657,7 +22657,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22888,7 +22888,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -23383,7 +23383,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -23548,7 +23548,7 @@
         <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -23779,7 +23779,7 @@
         <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>

--- a/docs/d/F/inyear.xlsx
+++ b/docs/d/F/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -7887,7 +7891,11 @@
       <c r="AB70" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC70" s="4" t="inlineStr"/>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -8913,7 +8921,11 @@
       <c r="AB80" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC80" s="4" t="inlineStr"/>
+      <c r="AC80" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -9830,7 +9842,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -10444,7 +10460,11 @@
       <c r="AB95" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC95" s="4" t="inlineStr"/>
+      <c r="AC95" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">

--- a/docs/d/F/inyear.xlsx
+++ b/docs/d/F/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 97 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 81 clubs short</t>
         </is>
       </c>
     </row>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>3</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>4</v>
       </c>
       <c r="W16" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X16" s="9" t="n">
         <v>1</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2457,8 +2457,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4610,8 +4610,8 @@
       <c r="Y38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" s="9" t="n">
-        <v>0</v>
+      <c r="Z38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA38" s="10" t="n">
         <v>1</v>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4816,8 +4816,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4917,8 +4917,8 @@
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA41" s="10" t="n">
         <v>1</v>
@@ -5408,7 +5408,7 @@
         <v>2</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="9" t="n">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5842,8 +5842,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6044,8 +6044,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8395,8 +8395,8 @@
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
+      <c r="Z75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
@@ -9813,7 +9813,7 @@
         <v>0</v>
       </c>
       <c r="S89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T89" s="9" t="n">
         <v>0</v>
@@ -9868,7 +9868,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9938,8 +9938,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -10942,7 +10942,7 @@
         <v>0</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" s="10" t="n">
         <v>1</v>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11061,8 +11061,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11259,8 +11259,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -11684,7 +11684,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11754,8 +11754,8 @@
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
@@ -16537,7 +16537,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16551,13 +16551,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
@@ -16607,8 +16607,8 @@
       <c r="Y157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" s="9" t="n">
-        <v>0</v>
+      <c r="Z157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA157" s="10" t="n">
         <v>1</v>
@@ -16977,7 +16977,7 @@
         <v>0</v>
       </c>
       <c r="Q161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R161" s="9" t="n">
         <v>0</v>
@@ -18657,7 +18657,7 @@
         </is>
       </c>
       <c r="P178" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q178" s="10" t="n">
         <v>2</v>
@@ -19012,7 +19012,7 @@
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>10</v>
@@ -19082,8 +19082,8 @@
       <c r="Y182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z182" s="9" t="n">
-        <v>0</v>
+      <c r="Z182" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA182" s="10" t="n">
         <v>1</v>
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>10</v>
@@ -19973,8 +19973,8 @@
       <c r="Y191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z191" s="9" t="n">
-        <v>0</v>
+      <c r="Z191" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA191" s="10" t="n">
         <v>1</v>
@@ -20794,7 +20794,7 @@
         </is>
       </c>
       <c r="E200" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F200" s="6" t="n">
         <v>10</v>
@@ -20864,8 +20864,8 @@
       <c r="Y200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z200" s="9" t="n">
-        <v>0</v>
+      <c r="Z200" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA200" s="10" t="n">
         <v>1</v>
@@ -21798,13 +21798,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>4</v>
       </c>
       <c r="W210" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X210" s="10" t="n">
         <v>6</v>
@@ -22279,7 +22279,7 @@
         </is>
       </c>
       <c r="E215" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F215" s="6" t="n">
         <v>10</v>
@@ -22349,8 +22349,8 @@
       <c r="Y215" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z215" s="9" t="n">
-        <v>0</v>
+      <c r="Z215" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA215" s="10" t="n">
         <v>1</v>
@@ -22545,7 +22545,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -22677,7 +22677,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22710,7 +22710,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -22776,7 +22776,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -22941,7 +22941,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -23040,7 +23040,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -23106,7 +23106,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -23139,7 +23139,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -23469,7 +23469,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -23634,7 +23634,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -23700,7 +23700,7 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -23766,7 +23766,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -23832,7 +23832,7 @@
         <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>

--- a/docs/d/F/inyear.xlsx
+++ b/docs/d/F/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 81 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 45 clubs short</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1023,8 +1023,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -1353,15 +1353,15 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7493</v>
+        <v>1600543</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>BergenMeisters Toastmasters Club</t>
+          <t>NAAAP-OC</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1402,31 +1402,31 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U7" s="10" t="n">
-        <v>3</v>
+      <c r="U7" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X7" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y7" s="9" t="n">
         <v>0</v>
@@ -1458,11 +1458,11 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1600543</v>
+        <v>6724</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>NAAAP-OC</t>
+          <t>Orange Toast Toastmasters Club</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
@@ -1518,8 +1518,8 @@
       <c r="S8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="10" t="n">
-        <v>1</v>
+      <c r="T8" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U8" s="9" t="n">
         <v>0</v>
@@ -1536,20 +1536,16 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1563,15 +1559,15 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6724</v>
+        <v>7493</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Orange Toast Toastmasters Club</t>
+          <t>Pathfinders Toastmasters Club</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1585,13 +1581,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1612,31 +1608,31 @@
         </is>
       </c>
       <c r="P9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X9" s="9" t="n">
-        <v>3</v>
+      <c r="X9" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>0</v>
@@ -1648,9 +1644,13 @@
         <v>1</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1843,8 +1843,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2239,8 +2239,8 @@
       <c r="U15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="9" t="n">
-        <v>3</v>
+      <c r="V15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2854,8 +2854,8 @@
       <c r="T21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U21" s="9" t="n">
-        <v>0</v>
+      <c r="U21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V21" s="9" t="n">
         <v>0</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="P22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3071,8 +3071,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3176,8 +3176,8 @@
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="9" t="n">
-        <v>0</v>
+      <c r="Z24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" s="10" t="n">
         <v>1</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4198,8 +4198,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="10" t="n">
         <v>1</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4509,8 +4509,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -5333,8 +5333,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="9" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5539,8 +5539,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6419,17 +6419,17 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="T56" s="10" t="n">
         <v>1</v>
       </c>
@@ -6443,7 +6443,7 @@
         <v>0</v>
       </c>
       <c r="X56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6549,8 +6549,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6745,14 +6745,14 @@
       <c r="W59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X59" s="9" t="n">
-        <v>0</v>
+      <c r="X59" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -6941,7 +6941,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="9" t="n">
         <v>0</v>
@@ -6961,8 +6961,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="9" t="n">
         <v>0</v>
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7368,13 +7368,13 @@
         <v>0</v>
       </c>
       <c r="X65" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7777,8 +7777,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8193,8 +8193,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -9118,8 +9118,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="9" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9306,8 +9306,8 @@
       <c r="S84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T84" s="9" t="n">
-        <v>0</v>
+      <c r="T84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U84" s="9" t="n">
         <v>0</v>
@@ -9324,8 +9324,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9530,8 +9530,8 @@
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9561,7 +9561,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9631,8 +9631,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9727,7 +9727,7 @@
         <v>0</v>
       </c>
       <c r="X88" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9803,8 +9803,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P89" s="9" t="n">
-        <v>2</v>
+      <c r="P89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>0</v>
@@ -10243,8 +10243,8 @@
       <c r="W93" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X93" s="9" t="n">
-        <v>3</v>
+      <c r="X93" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10350,8 +10350,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10863,8 +10863,8 @@
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -11288,7 +11288,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11358,8 +11358,8 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -11684,7 +11684,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11736,8 +11736,8 @@
       <c r="S108" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T108" s="9" t="n">
-        <v>0</v>
+      <c r="T108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U108" s="9" t="n">
         <v>0</v>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12033,8 +12033,8 @@
       <c r="S111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
@@ -12080,7 +12080,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12150,8 +12150,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12872,7 +12872,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12942,8 +12942,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -13070,7 +13070,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13140,8 +13140,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -14062,7 +14062,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14132,8 +14132,8 @@
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15023,8 +15023,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -16092,7 +16092,7 @@
         <v>0</v>
       </c>
       <c r="S152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T152" s="9" t="n">
         <v>0</v>
@@ -16141,7 +16141,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -16155,13 +16155,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -16199,8 +16199,8 @@
       <c r="U153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V153" s="9" t="n">
-        <v>3</v>
+      <c r="V153" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
@@ -16254,13 +16254,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>4</v>
       </c>
       <c r="W154" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X154" s="10" t="n">
         <v>6</v>
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="P157" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q157" s="9" t="n">
         <v>0</v>
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="P158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q158" s="9" t="n">
         <v>0</v>
@@ -16735,7 +16735,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16805,8 +16805,8 @@
       <c r="Y159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z159" s="9" t="n">
-        <v>0</v>
+      <c r="Z159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA159" s="10" t="n">
         <v>1</v>
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -17696,8 +17696,8 @@
       <c r="Y168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z168" s="9" t="n">
-        <v>0</v>
+      <c r="Z168" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA168" s="10" t="n">
         <v>1</v>
@@ -18319,7 +18319,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18389,8 +18389,8 @@
       <c r="Y175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z175" s="9" t="n">
-        <v>0</v>
+      <c r="Z175" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA175" s="10" t="n">
         <v>1</v>
@@ -19026,13 +19026,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>0</v>
       </c>
       <c r="V182" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W182" s="9" t="n">
         <v>0</v>
@@ -19507,7 +19507,7 @@
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -19577,8 +19577,8 @@
       <c r="Y187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z187" s="9" t="n">
-        <v>0</v>
+      <c r="Z187" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA187" s="10" t="n">
         <v>1</v>
@@ -19647,7 +19647,7 @@
         </is>
       </c>
       <c r="P188" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q188" s="10" t="n">
         <v>2</v>
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>10</v>
@@ -19775,8 +19775,8 @@
       <c r="Y189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z189" s="9" t="n">
-        <v>0</v>
+      <c r="Z189" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA189" s="10" t="n">
         <v>1</v>
@@ -20200,7 +20200,7 @@
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F194" s="6" t="n">
         <v>10</v>
@@ -20270,8 +20270,8 @@
       <c r="Y194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z194" s="9" t="n">
-        <v>0</v>
+      <c r="Z194" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA194" s="10" t="n">
         <v>1</v>
@@ -20695,7 +20695,7 @@
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F199" s="6" t="n">
         <v>10</v>
@@ -20765,8 +20765,8 @@
       <c r="Y199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z199" s="9" t="n">
-        <v>0</v>
+      <c r="Z199" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA199" s="10" t="n">
         <v>1</v>
@@ -20893,7 +20893,7 @@
         </is>
       </c>
       <c r="E201" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F201" s="6" t="n">
         <v>10</v>
@@ -20963,8 +20963,8 @@
       <c r="Y201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z201" s="9" t="n">
-        <v>0</v>
+      <c r="Z201" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA201" s="10" t="n">
         <v>1</v>
@@ -21627,7 +21627,7 @@
         </is>
       </c>
       <c r="P208" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q208" s="10" t="n">
         <v>2</v>
@@ -21825,7 +21825,7 @@
         </is>
       </c>
       <c r="P210" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q210" s="9" t="n">
         <v>1</v>
@@ -21834,7 +21834,7 @@
         <v>0</v>
       </c>
       <c r="S210" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T210" s="9" t="n">
         <v>0</v>
@@ -21883,7 +21883,7 @@
         </is>
       </c>
       <c r="E211" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F211" s="6" t="n">
         <v>10</v>
@@ -21953,8 +21953,8 @@
       <c r="Y211" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z211" s="9" t="n">
-        <v>0</v>
+      <c r="Z211" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA211" s="10" t="n">
         <v>1</v>
@@ -22446,7 +22446,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -22479,7 +22479,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -22512,7 +22512,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -22545,7 +22545,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -22578,7 +22578,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -22644,7 +22644,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -22677,7 +22677,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22743,7 +22743,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -22809,7 +22809,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -22842,7 +22842,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -22875,7 +22875,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -22908,7 +22908,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -22974,7 +22974,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -23007,7 +23007,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -23040,7 +23040,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -23073,7 +23073,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -23106,7 +23106,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -23139,7 +23139,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -23172,7 +23172,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -23238,7 +23238,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -23304,7 +23304,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -23370,7 +23370,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -23436,7 +23436,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -23502,7 +23502,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -23535,7 +23535,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -23601,7 +23601,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
@@ -23667,7 +23667,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -23700,7 +23700,7 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -23733,7 +23733,7 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -23766,7 +23766,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -23832,7 +23832,7 @@
         <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>

--- a/docs/d/F/inyear.xlsx
+++ b/docs/d/F/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 45 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 45 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1270,17 +1270,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1314,8 +1314,8 @@
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>3</v>
+      <c r="V6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1888,13 +1888,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2237,13 +2237,13 @@
         <v>1</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V15" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>7</v>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>4</v>
       </c>
       <c r="W16" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X16" s="9" t="n">
         <v>1</v>
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2708,17 +2708,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="8" t="n">
@@ -2813,13 +2813,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -3015,17 +3015,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -3423,13 +3423,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3524,13 +3524,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3553,8 +3553,8 @@
       <c r="P28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" s="9" t="n">
-        <v>1</v>
+      <c r="Q28" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R28" s="9" t="n">
         <v>0</v>
@@ -3562,8 +3562,8 @@
       <c r="S28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T28" s="9" t="n">
-        <v>0</v>
+      <c r="T28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U28" s="9" t="n">
         <v>0</v>
@@ -3726,13 +3726,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -4037,13 +4037,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4142,13 +4142,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4247,17 +4247,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4288,8 +4288,8 @@
       <c r="T35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U35" s="9" t="n">
-        <v>0</v>
+      <c r="U35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V35" s="9" t="n">
         <v>2</v>
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4352,17 +4352,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M36" s="8" t="n">
@@ -4396,8 +4396,8 @@
       <c r="U36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="9" t="n">
-        <v>3</v>
+      <c r="V36" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4554,13 +4554,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4655,17 +4655,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4700,7 +4700,7 @@
         <v>1</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4760,13 +4760,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4861,17 +4861,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M41" s="8" t="n">
@@ -4966,17 +4966,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -5071,13 +5071,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
         <v>0</v>
@@ -5221,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5378,13 +5378,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5685,13 +5685,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5786,13 +5786,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5887,13 +5887,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5988,13 +5988,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6089,13 +6089,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6190,17 +6190,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -6291,13 +6291,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6421,8 +6421,8 @@
       <c r="P56" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q56" s="9" t="n">
-        <v>1</v>
+      <c r="Q56" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6594,13 +6594,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6739,11 +6739,11 @@
       <c r="U59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="9" t="n">
-        <v>0</v>
+      <c r="V59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>7</v>
@@ -6800,13 +6800,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6905,13 +6905,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7006,17 +7006,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -7111,13 +7111,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7212,13 +7212,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>3</v>
+        <v>-20</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7418,13 +7418,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q66" s="9" t="n">
         <v>1</v>
@@ -7519,13 +7519,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7620,13 +7620,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7721,17 +7721,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7826,13 +7826,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>60</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>10</v>
+        <v>-18</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="P70" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>1</v>
@@ -7874,7 +7874,7 @@
         <v>4</v>
       </c>
       <c r="W70" s="10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X70" s="10" t="n">
         <v>6</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -8036,13 +8036,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8238,13 +8238,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8276,8 +8276,8 @@
       <c r="S74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T74" s="9" t="n">
-        <v>0</v>
+      <c r="T74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U74" s="9" t="n">
         <v>0</v>
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8339,17 +8339,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8377,8 +8377,8 @@
       <c r="S75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T75" s="9" t="n">
-        <v>0</v>
+      <c r="T75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U75" s="9" t="n">
         <v>0</v>
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8545,17 +8545,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8650,13 +8650,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8751,17 +8751,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8796,7 +8796,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8856,13 +8856,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8961,13 +8961,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9163,17 +9163,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -9268,13 +9268,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>6</v>
@@ -9373,13 +9373,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9575,13 +9575,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9676,13 +9676,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9777,13 +9777,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>5</v>
+        <v>-12</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9882,13 +9882,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9911,8 +9911,8 @@
       <c r="P90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" s="9" t="n">
-        <v>0</v>
+      <c r="Q90" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R90" s="9" t="n">
         <v>0</v>
@@ -9983,17 +9983,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -10088,17 +10088,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -10133,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -10193,13 +10193,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>4</v>
@@ -10294,13 +10294,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10395,17 +10395,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -10439,8 +10439,8 @@
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="9" t="n">
-        <v>3</v>
+      <c r="V95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10500,13 +10500,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10601,13 +10601,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10702,13 +10702,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10807,13 +10807,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>1</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10906,13 +10906,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>2</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11049,8 +11049,8 @@
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="9" t="n">
-        <v>1</v>
+      <c r="V101" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11104,13 +11104,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11203,13 +11203,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>0</v>
       </c>
       <c r="S103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T103" s="9" t="n">
         <v>0</v>
@@ -11347,7 +11347,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11401,17 +11401,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
@@ -11500,13 +11500,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11637,8 +11637,8 @@
       <c r="S107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T107" s="9" t="n">
-        <v>0</v>
+      <c r="T107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U107" s="9" t="n">
         <v>0</v>
@@ -11684,7 +11684,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11698,13 +11698,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11739,8 +11739,8 @@
       <c r="T108" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U108" s="9" t="n">
-        <v>0</v>
+      <c r="U108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V108" s="9" t="n">
         <v>1</v>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11941,7 +11941,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11995,13 +11995,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12094,17 +12094,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -12139,7 +12139,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12193,13 +12193,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12292,13 +12292,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -12391,13 +12391,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12534,8 +12534,8 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>0</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12589,17 +12589,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12634,7 +12634,7 @@
         <v>1</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12688,13 +12688,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12787,13 +12787,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12825,8 +12825,8 @@
       <c r="S119" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T119" s="9" t="n">
-        <v>0</v>
+      <c r="T119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U119" s="9" t="n">
         <v>0</v>
@@ -12886,13 +12886,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12985,17 +12985,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -13033,7 +13033,7 @@
         <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X121" s="10" t="n">
         <v>4</v>
@@ -13084,13 +13084,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13183,13 +13183,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>2</v>
+        <v>-14</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13209,12 +13209,12 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P123" s="9" t="n">
+      <c r="P123" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q123" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q123" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
       </c>
@@ -13227,11 +13227,11 @@
       <c r="U123" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V123" s="9" t="n">
-        <v>2</v>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X123" s="10" t="n">
         <v>6</v>
@@ -13282,13 +13282,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -13381,13 +13381,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>50</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-27</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -13482,13 +13482,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13581,13 +13581,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13878,13 +13878,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -13977,13 +13977,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q131" s="9" t="n">
         <v>1</v>
@@ -14019,13 +14019,13 @@
         <v>1</v>
       </c>
       <c r="U131" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V131" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>6</v>
@@ -14076,13 +14076,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -14175,17 +14175,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="8" t="n">
@@ -14274,13 +14274,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
@@ -14373,13 +14373,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>1</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -14571,17 +14571,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M137" s="8" t="n">
@@ -14670,13 +14670,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14769,13 +14769,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14868,13 +14868,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -15066,13 +15066,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15264,13 +15264,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15363,17 +15363,17 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L145" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M145" s="8" t="n">
@@ -15448,7 +15448,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15506,8 +15506,8 @@
       <c r="U146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V146" s="9" t="n">
-        <v>2</v>
+      <c r="V146" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -15660,17 +15660,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L148" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M148" s="8" t="n">
@@ -15759,13 +15759,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15858,13 +15858,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15885,16 +15885,16 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q150" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="Q150" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T150" s="9" t="n">
         <v>0</v>
@@ -15903,7 +15903,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
@@ -16056,13 +16056,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>4</v>
       </c>
       <c r="W153" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X153" s="9" t="n">
         <v>1</v>
@@ -16254,13 +16254,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>9</v>
+        <v>-2</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>4</v>
       </c>
       <c r="W154" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X154" s="10" t="n">
         <v>6</v>
@@ -16353,13 +16353,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -16452,13 +16452,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -16551,13 +16551,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
+        <v>-14</v>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="P157" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q157" s="9" t="n">
         <v>0</v>
@@ -16650,13 +16650,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>0</v>
       </c>
       <c r="V158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
@@ -16749,17 +16749,17 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L159" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M159" s="8" t="n">
@@ -16848,13 +16848,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L160" s="7" t="inlineStr">
         <is>
@@ -16947,13 +16947,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -17046,13 +17046,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>0</v>
       </c>
       <c r="V162" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
@@ -17145,13 +17145,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -17244,13 +17244,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -17343,13 +17343,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
@@ -17442,13 +17442,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>0</v>
       </c>
       <c r="V166" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
@@ -17541,13 +17541,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>0</v>
       </c>
       <c r="V167" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W167" s="9" t="n">
         <v>0</v>
@@ -17640,13 +17640,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>0</v>
       </c>
       <c r="V168" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W168" s="9" t="n">
         <v>0</v>
@@ -17739,13 +17739,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>0</v>
       </c>
       <c r="S169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T169" s="10" t="n">
         <v>1</v>
@@ -17838,13 +17838,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>0</v>
       </c>
       <c r="V170" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W170" s="9" t="n">
         <v>0</v>
@@ -17937,13 +17937,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
@@ -18036,13 +18036,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>0</v>
       </c>
       <c r="Q172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R172" s="9" t="n">
         <v>0</v>
@@ -18135,13 +18135,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
@@ -18234,13 +18234,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -18333,13 +18333,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -18432,13 +18432,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>0</v>
       </c>
       <c r="V177" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
@@ -18630,13 +18630,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
@@ -18729,17 +18729,17 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L179" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L179" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M179" s="8" t="n">
@@ -18828,13 +18828,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L180" s="7" t="inlineStr">
         <is>
@@ -18927,13 +18927,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>10</v>
@@ -19026,13 +19026,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -19070,11 +19070,11 @@
       <c r="U182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V182" s="9" t="n">
-        <v>2</v>
+      <c r="V182" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W182" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X182" s="10" t="n">
         <v>5</v>
@@ -19125,13 +19125,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
@@ -19224,17 +19224,17 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L184" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L184" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M184" s="8" t="n">
@@ -19422,13 +19422,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L186" s="7" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>4</v>
       </c>
       <c r="W186" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X186" s="10" t="n">
         <v>6</v>
@@ -19521,17 +19521,17 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L187" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L187" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M187" s="8" t="n">
@@ -19606,7 +19606,7 @@
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>10</v>
@@ -19620,13 +19620,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>60</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
@@ -19658,8 +19658,8 @@
       <c r="S188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T188" s="9" t="n">
-        <v>0</v>
+      <c r="T188" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U188" s="9" t="n">
         <v>0</v>
@@ -19668,7 +19668,7 @@
         <v>4</v>
       </c>
       <c r="W188" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X188" s="10" t="n">
         <v>7</v>
@@ -19719,17 +19719,17 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L189" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L189" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M189" s="8" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>0</v>
       </c>
       <c r="V190" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W190" s="9" t="n">
         <v>0</v>
@@ -19917,13 +19917,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>0</v>
       </c>
       <c r="V191" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W191" s="9" t="n">
         <v>0</v>
@@ -20016,13 +20016,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L192" s="7" t="inlineStr">
         <is>
@@ -20115,13 +20115,13 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
@@ -20214,17 +20214,17 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L194" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M194" s="8" t="n">
@@ -20313,13 +20313,13 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
@@ -20412,13 +20412,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L196" s="7" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>0</v>
       </c>
       <c r="V196" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W196" s="9" t="n">
         <v>0</v>
@@ -20497,7 +20497,7 @@
         </is>
       </c>
       <c r="E197" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F197" s="6" t="n">
         <v>10</v>
@@ -20511,13 +20511,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L197" s="4" t="inlineStr">
         <is>
@@ -20555,8 +20555,8 @@
       <c r="U197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V197" s="9" t="n">
-        <v>3</v>
+      <c r="V197" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W197" s="9" t="n">
         <v>0</v>
@@ -20610,13 +20610,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
@@ -20709,13 +20709,13 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
@@ -20808,13 +20808,13 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L200" s="7" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>0</v>
       </c>
       <c r="V201" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W201" s="9" t="n">
         <v>0</v>
@@ -21006,13 +21006,13 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L202" s="7" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="E203" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F203" s="6" t="n">
         <v>10</v>
@@ -21105,17 +21105,17 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L203" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L203" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M203" s="8" t="n">
@@ -21149,8 +21149,8 @@
       <c r="U203" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V203" s="9" t="n">
-        <v>3</v>
+      <c r="V203" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W203" s="9" t="n">
         <v>0</v>
@@ -21204,13 +21204,13 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L204" s="7" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         </is>
       </c>
       <c r="E205" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F205" s="6" t="n">
         <v>10</v>
@@ -21303,13 +21303,13 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
@@ -21347,8 +21347,8 @@
       <c r="U205" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V205" s="9" t="n">
-        <v>0</v>
+      <c r="V205" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W205" s="9" t="n">
         <v>0</v>
@@ -21429,7 +21429,7 @@
         </is>
       </c>
       <c r="P206" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q206" s="9" t="n">
         <v>0</v>
@@ -21501,17 +21501,17 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J207" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K207" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L207" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L207" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M207" s="8" t="n">
@@ -21546,7 +21546,7 @@
         <v>0</v>
       </c>
       <c r="V207" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W207" s="9" t="n">
         <v>0</v>
@@ -21600,13 +21600,13 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J208" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K208" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
@@ -21699,13 +21699,13 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
@@ -21798,13 +21798,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
@@ -21897,13 +21897,13 @@
         </is>
       </c>
       <c r="I211" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J211" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K211" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
@@ -21996,13 +21996,13 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J212" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K212" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L212" s="7" t="inlineStr">
         <is>
@@ -22194,13 +22194,13 @@
         </is>
       </c>
       <c r="I214" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J214" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K214" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L214" s="7" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="P214" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q214" s="9" t="n">
         <v>0</v>
@@ -22293,17 +22293,17 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J215" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K215" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L215" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L215" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M215" s="8" t="n">
@@ -22479,7 +22479,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -22494,7 +22494,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -22560,7 +22560,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -22593,7 +22593,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22611,7 +22611,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -22677,7 +22677,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22692,7 +22692,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -22725,7 +22725,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22809,7 +22809,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -22824,7 +22824,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -22842,7 +22842,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -22857,7 +22857,7 @@
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -22908,7 +22908,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -22923,7 +22923,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -22941,7 +22941,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -22956,7 +22956,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -22989,7 +22989,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -23040,7 +23040,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -23055,7 +23055,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -23073,7 +23073,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -23088,7 +23088,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -23106,7 +23106,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -23139,7 +23139,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -23154,7 +23154,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -23187,7 +23187,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -23205,7 +23205,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -23220,7 +23220,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -23238,13 +23238,13 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -23253,7 +23253,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -23319,7 +23319,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -23352,7 +23352,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -23403,7 +23403,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -23418,7 +23418,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -23436,7 +23436,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -23517,7 +23517,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -23616,7 +23616,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -23634,7 +23634,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -23649,7 +23649,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -23667,7 +23667,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -23682,7 +23682,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -23715,7 +23715,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -23733,7 +23733,7 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -23766,7 +23766,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -23781,7 +23781,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -23799,7 +23799,7 @@
         <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -23814,7 +23814,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -23847,7 +23847,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/F/inyear.xlsx
+++ b/docs/d/F/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/F/inyear.xlsx
+++ b/docs/d/F/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/F/inyear.xlsx
+++ b/docs/d/F/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/F/inyear.xlsx
+++ b/docs/d/F/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/F/inyear.xlsx
+++ b/docs/d/F/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 45 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 45 clubs short</t>
         </is>
       </c>
     </row>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1888,13 +1888,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1926,11 +1926,11 @@
       <c r="S12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v>0</v>
+      <c r="T12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V12" s="9" t="n">
         <v>1</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2033,8 +2033,8 @@
       <c r="U13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="9" t="n">
-        <v>3</v>
+      <c r="V13" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>0</v>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3970,8 +3970,8 @@
       <c r="S32" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T32" s="9" t="n">
-        <v>0</v>
+      <c r="T32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U32" s="9" t="n">
         <v>0</v>
@@ -3980,7 +3980,7 @@
         <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>6</v>
@@ -4277,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>0</v>
@@ -4861,13 +4861,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5001,8 +5001,8 @@
       <c r="R42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="9" t="n">
-        <v>1</v>
+      <c r="S42" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T42" s="9" t="n">
         <v>0</v>
@@ -5107,7 +5107,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" s="9" t="n">
         <v>0</v>
@@ -5988,13 +5988,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6800,13 +6800,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -7036,13 +7036,13 @@
         <v>1</v>
       </c>
       <c r="Q62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="9" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7111,13 +7111,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7155,8 +7155,8 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="9" t="n">
-        <v>3</v>
+      <c r="V63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7459,8 +7459,8 @@
       <c r="T66" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U66" s="9" t="n">
-        <v>0</v>
+      <c r="U66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V66" s="9" t="n">
         <v>1</v>
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -8339,13 +8339,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8650,13 +8650,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8856,13 +8856,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -9373,13 +9373,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q93" s="9" t="n">
         <v>0</v>
@@ -10395,13 +10395,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10500,13 +10500,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11005,13 +11005,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11046,8 +11046,8 @@
       <c r="T101" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U101" s="9" t="n">
-        <v>0</v>
+      <c r="U101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V101" s="10" t="n">
         <v>4</v>
@@ -11530,7 +11530,7 @@
         <v>3</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
@@ -11797,13 +11797,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11896,13 +11896,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13014,8 +13014,8 @@
       <c r="P121" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q121" s="9" t="n">
-        <v>1</v>
+      <c r="Q121" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -13282,13 +13282,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q130" s="9" t="n">
         <v>1</v>
@@ -13977,13 +13977,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>6</v>
@@ -14076,13 +14076,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -14571,13 +14571,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15389,8 +15389,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P145" s="9" t="n">
-        <v>2</v>
+      <c r="P145" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q145" s="9" t="n">
         <v>0</v>
@@ -15547,7 +15547,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15599,8 +15599,8 @@
       <c r="S147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T147" s="9" t="n">
-        <v>0</v>
+      <c r="T147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U147" s="9" t="n">
         <v>0</v>
@@ -15858,13 +15858,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -16155,17 +16155,17 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L153" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M153" s="8" t="n">
@@ -16254,13 +16254,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>2</v>
       </c>
       <c r="Q155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R155" s="9" t="n">
         <v>0</v>
@@ -17640,13 +17640,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -17739,13 +17739,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         </is>
       </c>
       <c r="P173" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q173" s="10" t="n">
         <v>2</v>
@@ -18333,13 +18333,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18432,13 +18432,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
@@ -18476,11 +18476,11 @@
       <c r="U176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V176" s="9" t="n">
-        <v>3</v>
+      <c r="V176" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W176" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X176" s="10" t="n">
         <v>7</v>
@@ -18729,17 +18729,17 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L179" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L179" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M179" s="8" t="n">
@@ -18777,7 +18777,7 @@
         <v>4</v>
       </c>
       <c r="W179" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X179" s="10" t="n">
         <v>7</v>
@@ -19260,7 +19260,7 @@
         <v>0</v>
       </c>
       <c r="S184" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T184" s="9" t="n">
         <v>0</v>
@@ -19521,13 +19521,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>0</v>
       </c>
       <c r="V187" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W187" s="9" t="n">
         <v>0</v>
@@ -19719,13 +19719,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>0</v>
       </c>
       <c r="S189" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T189" s="10" t="n">
         <v>1</v>
@@ -20736,7 +20736,7 @@
         </is>
       </c>
       <c r="P199" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q199" s="9" t="n">
         <v>0</v>
@@ -20808,13 +20808,13 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L200" s="7" t="inlineStr">
         <is>
@@ -21105,17 +21105,17 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L203" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-9</v>
+      </c>
+      <c r="L203" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M203" s="8" t="n">
@@ -21153,7 +21153,7 @@
         <v>4</v>
       </c>
       <c r="W203" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X203" s="9" t="n">
         <v>2</v>
@@ -21204,13 +21204,13 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L204" s="7" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         </is>
       </c>
       <c r="E205" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F205" s="6" t="n">
         <v>10</v>
@@ -21341,8 +21341,8 @@
       <c r="S205" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T205" s="9" t="n">
-        <v>0</v>
+      <c r="T205" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U205" s="9" t="n">
         <v>0</v>
@@ -21586,7 +21586,7 @@
         </is>
       </c>
       <c r="E208" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F208" s="6" t="n">
         <v>10</v>
@@ -21600,13 +21600,13 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J208" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K208" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
@@ -21635,17 +21635,17 @@
       <c r="R208" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S208" s="9" t="n">
-        <v>1</v>
+      <c r="S208" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T208" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U208" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V208" s="9" t="n">
         <v>3</v>
+      </c>
+      <c r="V208" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W208" s="9" t="n">
         <v>0</v>
@@ -21699,13 +21699,13 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -22644,7 +22644,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -22710,7 +22710,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -22842,7 +22842,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -22875,7 +22875,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -23106,7 +23106,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -23238,7 +23238,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -23403,7 +23403,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -23451,7 +23451,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -23601,7 +23601,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
@@ -23616,7 +23616,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -23781,7 +23781,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -23799,7 +23799,7 @@
         <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>

--- a/docs/d/F/inyear.xlsx
+++ b/docs/d/F/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 45 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 45 clubs short</t>
         </is>
       </c>
     </row>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>3</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="9" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V15" s="10" t="n">
         <v>4</v>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>4</v>
       </c>
       <c r="W16" s="10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X16" s="9" t="n">
         <v>1</v>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3565,8 +3565,8 @@
       <c r="T28" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U28" s="9" t="n">
-        <v>0</v>
+      <c r="U28" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V28" s="9" t="n">
         <v>2</v>
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="P30" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q30" s="9" t="n">
         <v>0</v>
@@ -4247,13 +4247,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4655,17 +4655,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4684,8 +4684,8 @@
       <c r="P39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" s="9" t="n">
-        <v>1</v>
+      <c r="Q39" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R39" s="9" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
         <v>1</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4760,13 +4760,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4996,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
@@ -6800,13 +6800,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7212,13 +7212,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7256,8 +7256,8 @@
       <c r="U64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="9" t="n">
-        <v>3</v>
+      <c r="V64" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -8650,13 +8650,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -9373,13 +9373,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9777,13 +9777,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9882,13 +9882,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9983,13 +9983,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>1</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -10294,13 +10294,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10500,13 +10500,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -11005,13 +11005,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>4</v>
@@ -11437,7 +11437,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" s="9" t="n">
         <v>0</v>
@@ -11500,13 +11500,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11797,13 +11797,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -12094,13 +12094,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12292,13 +12292,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12816,8 +12816,8 @@
       <c r="P119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" s="9" t="n">
-        <v>1</v>
+      <c r="Q119" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
@@ -12828,8 +12828,8 @@
       <c r="T119" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U119" s="9" t="n">
-        <v>0</v>
+      <c r="U119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V119" s="9" t="n">
         <v>0</v>
@@ -13210,7 +13210,7 @@
         </is>
       </c>
       <c r="P123" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q123" s="10" t="n">
         <v>2</v>
@@ -13282,13 +13282,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -13581,13 +13581,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -14673,10 +14673,10 @@
         <v>9</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15858,13 +15858,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15902,11 +15902,11 @@
       <c r="U150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V150" s="9" t="n">
-        <v>3</v>
+      <c r="V150" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>5</v>
@@ -16155,13 +16155,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>4</v>
       </c>
       <c r="W153" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X153" s="9" t="n">
         <v>1</v>
@@ -16254,13 +16254,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -16281,10 +16281,10 @@
         </is>
       </c>
       <c r="P154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R154" s="9" t="n">
         <v>0</v>
@@ -16302,7 +16302,7 @@
         <v>4</v>
       </c>
       <c r="W154" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X154" s="10" t="n">
         <v>6</v>
@@ -17046,13 +17046,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -17445,10 +17445,10 @@
         <v>7</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -17678,8 +17678,8 @@
       <c r="S168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T168" s="9" t="n">
-        <v>0</v>
+      <c r="T168" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U168" s="9" t="n">
         <v>0</v>
@@ -17690,8 +17690,8 @@
       <c r="W168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X168" s="9" t="n">
-        <v>3</v>
+      <c r="X168" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y168" s="9" t="n">
         <v>0</v>
@@ -18418,7 +18418,7 @@
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18470,11 +18470,11 @@
       <c r="S176" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U176" s="9" t="n">
-        <v>0</v>
+      <c r="T176" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U176" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V176" s="10" t="n">
         <v>4</v>
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>4</v>
       </c>
       <c r="W179" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X179" s="10" t="n">
         <v>7</v>
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>10</v>
@@ -19748,8 +19748,8 @@
       <c r="P189" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q189" s="9" t="n">
-        <v>1</v>
+      <c r="Q189" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R189" s="9" t="n">
         <v>0</v>
@@ -20893,7 +20893,7 @@
         </is>
       </c>
       <c r="E201" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F201" s="6" t="n">
         <v>10</v>
@@ -20907,17 +20907,17 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L201" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L201" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M201" s="8" t="n">
@@ -20951,11 +20951,11 @@
       <c r="U201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V201" s="9" t="n">
-        <v>2</v>
+      <c r="V201" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W201" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X201" s="9" t="n">
         <v>0</v>
@@ -21900,10 +21900,10 @@
         <v>8</v>
       </c>
       <c r="J211" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K211" s="4" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -22677,7 +22677,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22692,7 +22692,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -22875,7 +22875,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -23205,7 +23205,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -23436,7 +23436,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -23535,7 +23535,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -23601,13 +23601,13 @@
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -23667,7 +23667,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -23766,7 +23766,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -23781,7 +23781,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
